--- a/WC2026-entry-sheet.xlsx
+++ b/WC2026-entry-sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/varun_j_gupta_accenture_com/Documents/Code/fifa/asset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_CA31EA0BD542F0BE6A5D70164A5DCE3A974D0343" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C8EDEA0-BEEE-4328-851A-3B4F1F5AE971}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FB75C2-52DB-4A5C-A79D-0D0510FF8EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="168">
   <si>
     <t>🏆  FIFA WORLD CUP 2026 (USA · CANADA · MEXICO)  —  PREDICTOR GAME ENTRY SHEET  🏆</t>
   </si>
@@ -88,30 +88,9 @@
     <t>ROUND OF 32  (5 pts per correct team)</t>
   </si>
   <si>
-    <t>Fixture ref</t>
-  </si>
-  <si>
     <t>→ Team</t>
   </si>
   <si>
-    <t>R32-01: 1A v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-17: TBC</t>
-  </si>
-  <si>
-    <t>R32-02: 2A v 2B</t>
-  </si>
-  <si>
-    <t>R32-18: TBC</t>
-  </si>
-  <si>
-    <t>R32-03: 1B v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-19: TBC</t>
-  </si>
-  <si>
     <t>1st → 1A | 2nd → 2A | 3rd → 3A | 4th → 4A</t>
   </si>
   <si>
@@ -121,18 +100,6 @@
     <t>1st → 1C | 2nd → 2C | 3rd → 3C | 4th → 4C</t>
   </si>
   <si>
-    <t>R32-04: 2C v 2D</t>
-  </si>
-  <si>
-    <t>R32-20: TBC</t>
-  </si>
-  <si>
-    <t>R32-05: 1C v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-21: TBC</t>
-  </si>
-  <si>
     <t>GROUP D</t>
   </si>
   <si>
@@ -142,12 +109,6 @@
     <t>GROUP F</t>
   </si>
   <si>
-    <t>R32-06: 2E v 2F</t>
-  </si>
-  <si>
-    <t>R32-22: TBC</t>
-  </si>
-  <si>
     <t>United States</t>
   </si>
   <si>
@@ -166,12 +127,6 @@
     <t>Japan</t>
   </si>
   <si>
-    <t>R32-07: 1D v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-23: TBC</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -190,36 +145,6 @@
     <t>Tunisia</t>
   </si>
   <si>
-    <t>R32-08: 2G v 2H</t>
-  </si>
-  <si>
-    <t>R32-24: TBC</t>
-  </si>
-  <si>
-    <t>R32-09: 1E v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-25: TBC</t>
-  </si>
-  <si>
-    <t>R32-10: 2I v 2J</t>
-  </si>
-  <si>
-    <t>R32-26: TBC</t>
-  </si>
-  <si>
-    <t>R32-11: 1F v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-27: TBC</t>
-  </si>
-  <si>
-    <t>R32-12: 2K v 2L</t>
-  </si>
-  <si>
-    <t>R32-28: TBC</t>
-  </si>
-  <si>
     <t>1st → 1D | 2nd → 2D | 3rd → 3D | 4th → 4D</t>
   </si>
   <si>
@@ -229,18 +154,6 @@
     <t>1st → 1F | 2nd → 2F | 3rd → 3F | 4th → 4F</t>
   </si>
   <si>
-    <t>R32-13: 1G v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-29: TBC</t>
-  </si>
-  <si>
-    <t>R32-14: 1H v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-30: TBC</t>
-  </si>
-  <si>
     <t>GROUP G</t>
   </si>
   <si>
@@ -250,12 +163,6 @@
     <t>GROUP I</t>
   </si>
   <si>
-    <t>R32-15: 1I v Best 3rd</t>
-  </si>
-  <si>
-    <t>R32-31: TBC</t>
-  </si>
-  <si>
     <t>Belgium</t>
   </si>
   <si>
@@ -274,12 +181,6 @@
     <t>Senegal</t>
   </si>
   <si>
-    <t>R32-16: 1J v 1K</t>
-  </si>
-  <si>
-    <t>R32-32: TBC</t>
-  </si>
-  <si>
     <t>Iran</t>
   </si>
   <si>
@@ -301,18 +202,6 @@
     <t>ROUND OF 16  (10 pts per correct team)</t>
   </si>
   <si>
-    <t>R16-01: Winner R32-01 v R32-02</t>
-  </si>
-  <si>
-    <t>R16-09: Winner R32-17 v R32-18</t>
-  </si>
-  <si>
-    <t>R16-02: Winner R32-03 v R32-04</t>
-  </si>
-  <si>
-    <t>R16-10: Winner R32-19 v R32-20</t>
-  </si>
-  <si>
     <t>1st → 1G | 2nd → 2G | 3rd → 3G | 4th → 4G</t>
   </si>
   <si>
@@ -322,18 +211,6 @@
     <t>1st → 1I | 2nd → 2I | 3rd → 3I | 4th → 4I</t>
   </si>
   <si>
-    <t>R16-03: Winner R32-05 v R32-06</t>
-  </si>
-  <si>
-    <t>R16-11: Winner R32-21 v R32-22</t>
-  </si>
-  <si>
-    <t>R16-04: Winner R32-07 v R32-08</t>
-  </si>
-  <si>
-    <t>R16-12: Winner R32-23 v R32-24</t>
-  </si>
-  <si>
     <t>GROUP J</t>
   </si>
   <si>
@@ -343,12 +220,6 @@
     <t>GROUP L</t>
   </si>
   <si>
-    <t>R16-05: Winner R32-09 v R32-10</t>
-  </si>
-  <si>
-    <t>R16-13: Winner R32-25 v R32-26</t>
-  </si>
-  <si>
     <t>Argentina</t>
   </si>
   <si>
@@ -367,12 +238,6 @@
     <t>Croatia</t>
   </si>
   <si>
-    <t>R16-06: Winner R32-11 v R32-12</t>
-  </si>
-  <si>
-    <t>R16-14: Winner R32-27 v R32-28</t>
-  </si>
-  <si>
     <t>Austria</t>
   </si>
   <si>
@@ -391,18 +256,6 @@
     <t>Panama</t>
   </si>
   <si>
-    <t>R16-07: Winner R32-13 v R32-14</t>
-  </si>
-  <si>
-    <t>R16-15: Winner R32-29 v R32-30</t>
-  </si>
-  <si>
-    <t>R16-08: Winner R32-15 v R32-16</t>
-  </si>
-  <si>
-    <t>R16-16: Winner R32-31 v R32-32</t>
-  </si>
-  <si>
     <t>QUARTER-FINALS  (15 pts per correct team)</t>
   </si>
   <si>
@@ -415,54 +268,12 @@
     <t>1st → 1L | 2nd → 2L | 3rd → 3L | 4th → 4L</t>
   </si>
   <si>
-    <t>QF-1: Winner R16-01 v R16-05</t>
-  </si>
-  <si>
-    <t>QF-5: Winner R16-09 v R16-13</t>
-  </si>
-  <si>
-    <t>QF-2: Winner R16-02 v R16-06</t>
-  </si>
-  <si>
-    <t>QF-6: Winner R16-10 v R16-14</t>
-  </si>
-  <si>
-    <t>QF-3: Winner R16-03 v R16-07</t>
-  </si>
-  <si>
-    <t>QF-7: Winner R16-11 v R16-15</t>
-  </si>
-  <si>
-    <t>QF-4: Winner R16-04 v R16-08</t>
-  </si>
-  <si>
-    <t>QF-8: Winner R16-12 v R16-16</t>
-  </si>
-  <si>
     <t>SEMI-FINALS  (20 pts per correct team)</t>
   </si>
   <si>
-    <t>SF-1: Winner QF-1 v QF-3</t>
-  </si>
-  <si>
-    <t>SF-3: Winner QF-5 v QF-7</t>
-  </si>
-  <si>
-    <t>SF-2: Winner QF-2 v QF-4</t>
-  </si>
-  <si>
-    <t>SF-4: Winner QF-6 v QF-8</t>
-  </si>
-  <si>
     <t>FINAL  (25 pts per correct team)</t>
   </si>
   <si>
-    <t>Final Finalist: Winner of SF-1</t>
-  </si>
-  <si>
-    <t>Final Finalist: Winner of SF-3</t>
-  </si>
-  <si>
     <t>WORLD CUP WINNER  🏆  (30 pts)</t>
   </si>
   <si>
@@ -478,15 +289,6 @@
     <t>QUICK SCORING REFERENCE</t>
   </si>
   <si>
-    <t>Group Stage – correct result</t>
-  </si>
-  <si>
-    <t>3 pts</t>
-  </si>
-  <si>
-    <t>Group Stage – correct result + exact score</t>
-  </si>
-  <si>
     <t>5 pts</t>
   </si>
   <si>
@@ -517,9 +319,6 @@
     <t>25 pts</t>
   </si>
   <si>
-    <t>World Cup Winner</t>
-  </si>
-  <si>
     <t>30 pts</t>
   </si>
   <si>
@@ -527,13 +326,211 @@
   </si>
   <si>
     <t>HANDLE</t>
+  </si>
+  <si>
+    <t>World Cup Winner - if correct</t>
+  </si>
+  <si>
+    <t>Group Stage – correct result (+ exact score)</t>
+  </si>
+  <si>
+    <t>3 pts (5pts total)</t>
+  </si>
+  <si>
+    <t>M73: 2A</t>
+  </si>
+  <si>
+    <t>M73: 2B</t>
+  </si>
+  <si>
+    <t>M74: 1E</t>
+  </si>
+  <si>
+    <t>M74: 3A/B/C/D/F</t>
+  </si>
+  <si>
+    <t>M75: 1F</t>
+  </si>
+  <si>
+    <t>M75: 2C</t>
+  </si>
+  <si>
+    <t>M76: 1C</t>
+  </si>
+  <si>
+    <t>M76: 2F</t>
+  </si>
+  <si>
+    <t>M77: 3C/D/F/G/H</t>
+  </si>
+  <si>
+    <t>M78: 2E</t>
+  </si>
+  <si>
+    <t>M78: 2I</t>
+  </si>
+  <si>
+    <t>M77: 1I</t>
+  </si>
+  <si>
+    <t>M79: 1A</t>
+  </si>
+  <si>
+    <t>M79: 3C/E/F/H/I</t>
+  </si>
+  <si>
+    <t>M80: 3E/H/I/J/K</t>
+  </si>
+  <si>
+    <t>M81: 1D</t>
+  </si>
+  <si>
+    <t>M81: 3B/E/F/I/J</t>
+  </si>
+  <si>
+    <t>M82: 1G</t>
+  </si>
+  <si>
+    <t>M82: 3A/E/H/I/J</t>
+  </si>
+  <si>
+    <t>M83: 2K</t>
+  </si>
+  <si>
+    <t>M83: 2L</t>
+  </si>
+  <si>
+    <t>M84: 1H</t>
+  </si>
+  <si>
+    <t>M84: 2J</t>
+  </si>
+  <si>
+    <t>M85: 1B</t>
+  </si>
+  <si>
+    <t>M85: 3E/F/G/I/J</t>
+  </si>
+  <si>
+    <t>M86: 1J</t>
+  </si>
+  <si>
+    <t>M86: 2H</t>
+  </si>
+  <si>
+    <t>M87: 1K</t>
+  </si>
+  <si>
+    <t>M87: 3D/E/I/J/L</t>
+  </si>
+  <si>
+    <t>M88: 2D</t>
+  </si>
+  <si>
+    <t>M88: 2G</t>
+  </si>
+  <si>
+    <t>M80: 1L</t>
+  </si>
+  <si>
+    <t>M89: Winner M74</t>
+  </si>
+  <si>
+    <t>M89: Winner M77</t>
+  </si>
+  <si>
+    <t>M90: Winner M73</t>
+  </si>
+  <si>
+    <t>M90: Winner M75</t>
+  </si>
+  <si>
+    <t>M91: Winner M76</t>
+  </si>
+  <si>
+    <t>M91: Winner M78</t>
+  </si>
+  <si>
+    <t>M92: Winner M79</t>
+  </si>
+  <si>
+    <t>M92: Winner M80</t>
+  </si>
+  <si>
+    <t>M93: Winner M83</t>
+  </si>
+  <si>
+    <t>M93: Winner M84</t>
+  </si>
+  <si>
+    <t>M94: Winner M81</t>
+  </si>
+  <si>
+    <t>M94: Winner M82</t>
+  </si>
+  <si>
+    <t>M95: Winner M86</t>
+  </si>
+  <si>
+    <t>M95: Winner M88</t>
+  </si>
+  <si>
+    <t>M96: Winner M85</t>
+  </si>
+  <si>
+    <t>M96: Winner M87</t>
+  </si>
+  <si>
+    <t>M97: Winner M89</t>
+  </si>
+  <si>
+    <t>M97: Winner M90</t>
+  </si>
+  <si>
+    <t>M98: Winner M93</t>
+  </si>
+  <si>
+    <t>M98: Winner M94</t>
+  </si>
+  <si>
+    <t>M99: Winner M91</t>
+  </si>
+  <si>
+    <t>M99: Winner M92</t>
+  </si>
+  <si>
+    <t>M100: Winner M95</t>
+  </si>
+  <si>
+    <t>M100: Winner M96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M101: Winner M97 </t>
+  </si>
+  <si>
+    <t>M102: Winner M99</t>
+  </si>
+  <si>
+    <t>M101: Winner M98</t>
+  </si>
+  <si>
+    <t>M102: Winner M100</t>
+  </si>
+  <si>
+    <t>M104: Winner M101</t>
+  </si>
+  <si>
+    <t>M104: Winner M102</t>
+  </si>
+  <si>
+    <t>Fixture ref (Match: Team)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,12 +542,6 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFC9A227"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -612,11 +603,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F3864"/>
@@ -643,6 +629,46 @@
       <sz val="9"/>
       <color rgb="FF2E74B5"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF2E74B5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -708,7 +734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -775,95 +801,235 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1171,130 +1337,131 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:X66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="1.44140625" customWidth="1"/>
+    <col min="6" max="6" width="1.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="10" width="5" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="1.44140625" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="16" width="5" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="1.44140625" customWidth="1"/>
+    <col min="18" max="18" width="1.42578125" customWidth="1"/>
     <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="21" width="5" customWidth="1"/>
+    <col min="20" max="20" width="6.42578125" customWidth="1"/>
+    <col min="21" max="21" width="19.85546875" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="1.44140625" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="23" max="23" width="6" customWidth="1"/>
+    <col min="24" max="24" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:24" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-    </row>
-    <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+    </row>
+    <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="25" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="26"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="S3" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="T3" s="28"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="W3" s="28"/>
-      <c r="X3" s="29"/>
-    </row>
-    <row r="4" spans="1:24" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="T2" s="27"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="30"/>
+    </row>
+    <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="T3" s="47"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="W3" s="40"/>
+      <c r="X3" s="41"/>
+    </row>
+    <row r="4" spans="1:24" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="G4" s="11" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="15"/>
+      <c r="G4" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="M4" s="11" t="s">
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="15"/>
+      <c r="M4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="S4" s="22" t="s">
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="15"/>
+      <c r="S4" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-    </row>
-    <row r="5" spans="1:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T4" s="45"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="46"/>
+    </row>
+    <row r="5" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1328,16 +1495,16 @@
       <c r="Q5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-    </row>
-    <row r="6" spans="1:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="17"/>
+    </row>
+    <row r="6" spans="1:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1371,16 +1538,16 @@
       <c r="Q6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="S6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-    </row>
-    <row r="7" spans="1:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+    </row>
+    <row r="7" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -1414,22 +1581,22 @@
       <c r="Q7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="T7" s="15"/>
+      <c r="U7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="T7" s="10"/>
-      <c r="U7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V7" s="9" t="s">
+      <c r="V7" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="W7" s="15"/>
+      <c r="X7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W7" s="10"/>
-      <c r="X7" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -1463,18 +1630,18 @@
       <c r="Q8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T8" s="10"/>
+      <c r="S8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="T8" s="19"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="W8" s="10"/>
+      <c r="V8" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="W8" s="19"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1508,18 +1675,18 @@
       <c r="Q9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="T9" s="10"/>
+      <c r="S9" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="T9" s="19"/>
       <c r="U9" s="2"/>
-      <c r="V9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="W9" s="10"/>
+      <c r="V9" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="W9" s="19"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1553,98 +1720,98 @@
       <c r="Q10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S10" s="12" t="s">
+      <c r="S10" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="T10" s="19"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="W10" s="19"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="15"/>
+      <c r="G11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="15"/>
+      <c r="M11" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="15"/>
+      <c r="S11" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="T11" s="19"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="W11" s="19"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S12" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="W12" s="19"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="15"/>
+      <c r="G13" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="15"/>
+      <c r="M13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="10"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="12" t="s">
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="15"/>
+      <c r="S13" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="T13" s="19"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="W13" s="19"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="W10" s="10"/>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="G11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="M11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="S11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="10"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="W11" s="10"/>
-      <c r="X11" s="2"/>
-    </row>
-    <row r="12" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="T12" s="10"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" s="10"/>
-      <c r="X12" s="2"/>
-    </row>
-    <row r="13" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="G13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="M13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="S13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T13" s="10"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="W13" s="10"/>
-      <c r="X13" s="2"/>
-    </row>
-    <row r="14" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="3" t="s">
@@ -1652,10 +1819,10 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="3" t="s">
@@ -1663,10 +1830,10 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="3" t="s">
@@ -1674,22 +1841,22 @@
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="S14" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="T14" s="19"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="W14" s="10"/>
+      <c r="V14" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="W14" s="19"/>
       <c r="X14" s="2"/>
     </row>
-    <row r="15" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="3" t="s">
@@ -1697,10 +1864,10 @@
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="3" t="s">
@@ -1708,10 +1875,10 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="3" t="s">
@@ -1719,22 +1886,22 @@
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="S15" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="T15" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="T15" s="19"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="W15" s="10"/>
+      <c r="V15" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="W15" s="19"/>
       <c r="X15" s="2"/>
     </row>
-    <row r="16" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="3" t="s">
@@ -1742,10 +1909,10 @@
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="3" t="s">
@@ -1753,10 +1920,10 @@
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="3" t="s">
@@ -1764,22 +1931,22 @@
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="S16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="T16" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="S16" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="T16" s="19"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="W16" s="10"/>
+      <c r="V16" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="W16" s="19"/>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="3" t="s">
@@ -1787,10 +1954,10 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="3" t="s">
@@ -1798,10 +1965,10 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="4" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="3" t="s">
@@ -1809,22 +1976,22 @@
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S17" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="T17" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="S17" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="T17" s="19"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="W17" s="10"/>
+      <c r="V17" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="W17" s="19"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="3" t="s">
@@ -1832,10 +1999,10 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="3" t="s">
@@ -1843,10 +2010,10 @@
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="3" t="s">
@@ -1854,22 +2021,22 @@
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S18" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="T18" s="10"/>
+        <v>33</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="T18" s="19"/>
       <c r="U18" s="2"/>
-      <c r="V18" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="W18" s="10"/>
+      <c r="V18" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="W18" s="19"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="3" t="s">
@@ -1877,10 +2044,10 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
@@ -1888,10 +2055,10 @@
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="3" t="s">
@@ -1899,100 +2066,100 @@
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="T19" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="S19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="T19" s="19"/>
       <c r="U19" s="2"/>
-      <c r="V19" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="W19" s="10"/>
+      <c r="V19" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="W19" s="19"/>
       <c r="X19" s="2"/>
     </row>
-    <row r="20" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="G20" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="M20" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="S20" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="T20" s="10"/>
+    <row r="20" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="15"/>
+      <c r="G20" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="15"/>
+      <c r="M20" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="15"/>
+      <c r="S20" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="T20" s="19"/>
       <c r="U20" s="2"/>
-      <c r="V20" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="W20" s="10"/>
+      <c r="V20" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="W20" s="19"/>
       <c r="X20" s="2"/>
     </row>
-    <row r="21" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S21" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T21" s="10"/>
+    <row r="21" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S21" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="T21" s="19"/>
       <c r="U21" s="2"/>
-      <c r="V21" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="W21" s="10"/>
+      <c r="V21" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="W21" s="19"/>
       <c r="X21" s="2"/>
     </row>
-    <row r="22" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="G22" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="M22" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="S22" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="T22" s="10"/>
+    <row r="22" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="15"/>
+      <c r="G22" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="15"/>
+      <c r="M22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="15"/>
+      <c r="S22" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="T22" s="19"/>
       <c r="U22" s="2"/>
-      <c r="V22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="W22" s="10"/>
+      <c r="V22" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="W22" s="19"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="3" t="s">
@@ -2000,10 +2167,10 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="4" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="3" t="s">
@@ -2011,10 +2178,10 @@
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="4" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="3" t="s">
@@ -2022,22 +2189,22 @@
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="T23" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="S23" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="T23" s="19"/>
       <c r="U23" s="2"/>
-      <c r="V23" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="W23" s="10"/>
+      <c r="V23" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="W23" s="19"/>
       <c r="X23" s="2"/>
     </row>
-    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="3" t="s">
@@ -2045,10 +2212,10 @@
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="3" t="s">
@@ -2056,10 +2223,10 @@
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="4" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="3" t="s">
@@ -2067,12 +2234,12 @@
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="3" t="s">
@@ -2080,10 +2247,10 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="4" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="3" t="s">
@@ -2091,10 +2258,10 @@
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="3" t="s">
@@ -2102,20 +2269,20 @@
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-    </row>
-    <row r="26" spans="1:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="S25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="T25" s="17"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="17"/>
+    </row>
+    <row r="26" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="3" t="s">
@@ -2123,10 +2290,10 @@
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="4" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="3" t="s">
@@ -2134,10 +2301,10 @@
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="4" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="3" t="s">
@@ -2145,26 +2312,26 @@
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="S26" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="S26" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="T26" s="15"/>
+      <c r="U26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T26" s="10"/>
-      <c r="U26" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V26" s="9" t="s">
+      <c r="V26" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="W26" s="15"/>
+      <c r="X26" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W26" s="10"/>
-      <c r="X26" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="3" t="s">
@@ -2172,10 +2339,10 @@
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="4" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="3" t="s">
@@ -2183,10 +2350,10 @@
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="4" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="3" t="s">
@@ -2194,22 +2361,22 @@
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="T27" s="10"/>
+        <v>51</v>
+      </c>
+      <c r="S27" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="T27" s="19"/>
       <c r="U27" s="2"/>
-      <c r="V27" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="W27" s="10"/>
+      <c r="V27" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="W27" s="19"/>
       <c r="X27" s="2"/>
     </row>
-    <row r="28" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="3" t="s">
@@ -2217,10 +2384,10 @@
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="4" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="3" t="s">
@@ -2228,10 +2395,10 @@
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="4" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="3" t="s">
@@ -2239,100 +2406,100 @@
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="S28" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="T28" s="10"/>
+        <v>57</v>
+      </c>
+      <c r="S28" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="T28" s="15"/>
       <c r="U28" s="2"/>
-      <c r="V28" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="W28" s="10"/>
+      <c r="V28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="W28" s="15"/>
       <c r="X28" s="2"/>
     </row>
-    <row r="29" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="G29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="M29" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="S29" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="T29" s="10"/>
+    <row r="29" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="15"/>
+      <c r="G29" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="15"/>
+      <c r="M29" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="15"/>
+      <c r="S29" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="T29" s="23"/>
       <c r="U29" s="2"/>
-      <c r="V29" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="W29" s="10"/>
+      <c r="V29" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="W29" s="23"/>
       <c r="X29" s="2"/>
     </row>
-    <row r="30" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S30" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="T30" s="10"/>
+    <row r="30" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S30" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="T30" s="23"/>
       <c r="U30" s="2"/>
-      <c r="V30" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="W30" s="10"/>
+      <c r="V30" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="W30" s="23"/>
       <c r="X30" s="2"/>
     </row>
-    <row r="31" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="G31" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="M31" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="S31" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="T31" s="10"/>
+    <row r="31" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="G31" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="M31" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="S31" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="T31" s="23"/>
       <c r="U31" s="2"/>
-      <c r="V31" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="W31" s="10"/>
+      <c r="V31" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="W31" s="23"/>
       <c r="X31" s="2"/>
     </row>
-    <row r="32" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="3" t="s">
@@ -2340,10 +2507,10 @@
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="4" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="3" t="s">
@@ -2351,10 +2518,10 @@
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="4" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="3" t="s">
@@ -2362,22 +2529,22 @@
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="S32" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="T32" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="S32" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="T32" s="23"/>
       <c r="U32" s="2"/>
-      <c r="V32" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="W32" s="10"/>
+      <c r="V32" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="W32" s="23"/>
       <c r="X32" s="2"/>
     </row>
-    <row r="33" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="3" t="s">
@@ -2385,10 +2552,10 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="4" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="3" t="s">
@@ -2396,10 +2563,10 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="4" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="3" t="s">
@@ -2407,22 +2574,22 @@
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="S33" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="T33" s="10"/>
+        <v>77</v>
+      </c>
+      <c r="S33" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="T33" s="23"/>
       <c r="U33" s="2"/>
-      <c r="V33" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="W33" s="10"/>
+      <c r="V33" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="W33" s="23"/>
       <c r="X33" s="2"/>
     </row>
-    <row r="34" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="3" t="s">
@@ -2430,10 +2597,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="4" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="3" t="s">
@@ -2441,10 +2608,10 @@
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="4" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="3" t="s">
@@ -2452,22 +2619,22 @@
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="S34" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="T34" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="S34" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="T34" s="23"/>
       <c r="U34" s="2"/>
-      <c r="V34" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="W34" s="10"/>
+      <c r="V34" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="W34" s="23"/>
       <c r="X34" s="2"/>
     </row>
-    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="3" t="s">
@@ -2475,10 +2642,10 @@
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="4" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="3" t="s">
@@ -2486,10 +2653,10 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="4" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="3" t="s">
@@ -2497,12 +2664,12 @@
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="3" t="s">
@@ -2510,10 +2677,10 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="4" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="3" t="s">
@@ -2521,10 +2688,10 @@
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="4" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="3" t="s">
@@ -2532,20 +2699,20 @@
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="S36" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10"/>
-    </row>
-    <row r="37" spans="1:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="S36" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="T36" s="17"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="17"/>
+    </row>
+    <row r="37" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="3" t="s">
@@ -2553,10 +2720,10 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="4" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="3" t="s">
@@ -2564,10 +2731,10 @@
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="4" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="3" t="s">
@@ -2575,340 +2742,323 @@
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="S37" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="S37" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="T37" s="15"/>
+      <c r="U37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T37" s="10"/>
-      <c r="U37" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V37" s="9" t="s">
+      <c r="V37" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="W37" s="15"/>
+      <c r="X37" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W37" s="10"/>
-      <c r="X37" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="G38" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="M38" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="S38" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="T38" s="10"/>
+    </row>
+    <row r="38" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="15"/>
+      <c r="G38" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="15"/>
+      <c r="M38" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="15"/>
+      <c r="S38" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="T38" s="19"/>
       <c r="U38" s="2"/>
-      <c r="V38" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="W38" s="10"/>
+      <c r="V38" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="W38" s="19"/>
       <c r="X38" s="2"/>
     </row>
-    <row r="39" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S39" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="T39" s="10"/>
+    <row r="39" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S39" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="T39" s="19"/>
       <c r="U39" s="2"/>
-      <c r="V39" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="W39" s="10"/>
+      <c r="V39" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="W39" s="19"/>
       <c r="X39" s="2"/>
     </row>
-    <row r="40" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S40" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="T40" s="10"/>
+    <row r="40" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S40" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="T40" s="19"/>
       <c r="U40" s="2"/>
-      <c r="V40" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="W40" s="10"/>
+      <c r="V40" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="W40" s="19"/>
       <c r="X40" s="2"/>
     </row>
-    <row r="41" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S41" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="T41" s="10"/>
+    <row r="41" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S41" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="T41" s="19"/>
       <c r="U41" s="2"/>
-      <c r="V41" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="W41" s="10"/>
+      <c r="V41" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="W41" s="19"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="43" spans="1:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S43" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10"/>
-    </row>
-    <row r="44" spans="1:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S44" s="9" t="s">
+    <row r="43" spans="1:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S43" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+    </row>
+    <row r="44" spans="1:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S44" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="T44" s="15"/>
+      <c r="U44" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T44" s="10"/>
-      <c r="U44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V44" s="9" t="s">
+      <c r="V44" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="W44" s="15"/>
+      <c r="X44" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="W44" s="10"/>
-      <c r="X44" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S45" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="T45" s="10"/>
+    </row>
+    <row r="45" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S45" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="T45" s="19"/>
       <c r="U45" s="2"/>
-      <c r="V45" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="W45" s="10"/>
+      <c r="V45" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="W45" s="19"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S46" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="T46" s="10"/>
+    <row r="46" spans="1:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S46" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="T46" s="15"/>
       <c r="U46" s="2"/>
-      <c r="V46" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="W46" s="10"/>
+      <c r="V46" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="W46" s="15"/>
       <c r="X46" s="2"/>
     </row>
-    <row r="48" spans="1:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S48" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="T48" s="10"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
-      <c r="X48" s="10"/>
-    </row>
-    <row r="49" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S49" s="9" t="s">
+    <row r="48" spans="1:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S48" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+    </row>
+    <row r="49" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S49" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="T49" s="15"/>
+      <c r="U49" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="T49" s="10"/>
-      <c r="U49" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="V49" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="W49" s="10"/>
-      <c r="X49" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="19:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S50" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="T50" s="10"/>
+      <c r="V49" s="39"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="10"/>
+    </row>
+    <row r="50" spans="19:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S50" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="T50" s="19"/>
       <c r="U50" s="2"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-    </row>
-    <row r="51" spans="19:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S51" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="T51" s="10"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+    </row>
+    <row r="51" spans="19:24" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S51" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="T51" s="19"/>
       <c r="U51" s="2"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="X51" s="10"/>
-    </row>
-    <row r="53" spans="19:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S53" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-    </row>
-    <row r="54" spans="19:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S54" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+    </row>
+    <row r="53" spans="19:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S53" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="T53" s="21"/>
+      <c r="U53" s="21"/>
+      <c r="V53" s="21"/>
+      <c r="W53" s="21"/>
+      <c r="X53" s="15"/>
+    </row>
+    <row r="54" spans="19:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S54" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="T54" s="21"/>
+      <c r="U54" s="21"/>
+      <c r="V54" s="21"/>
+      <c r="W54" s="15"/>
       <c r="X54" s="6"/>
     </row>
-    <row r="56" spans="19:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S56" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-    </row>
-    <row r="57" spans="19:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S57" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
+    <row r="56" spans="19:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S56" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="T56" s="21"/>
+      <c r="U56" s="21"/>
+      <c r="V56" s="21"/>
+      <c r="W56" s="21"/>
+      <c r="X56" s="15"/>
+    </row>
+    <row r="57" spans="19:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S57" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="T57" s="21"/>
+      <c r="U57" s="21"/>
+      <c r="V57" s="21"/>
+      <c r="W57" s="15"/>
       <c r="X57" s="7"/>
     </row>
-    <row r="59" spans="19:24" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S59" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-    </row>
-    <row r="60" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S60" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="T60" s="10"/>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="61" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S61" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
+    <row r="59" spans="19:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S59" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="T59" s="21"/>
+      <c r="U59" s="21"/>
+      <c r="V59" s="21"/>
+      <c r="W59" s="21"/>
+      <c r="X59" s="15"/>
+    </row>
+    <row r="60" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S60" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="T60" s="21"/>
+      <c r="U60" s="21"/>
+      <c r="V60" s="21"/>
+      <c r="W60" s="15"/>
+      <c r="X60" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S61" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="T61" s="21"/>
+      <c r="U61" s="21"/>
+      <c r="V61" s="21"/>
+      <c r="W61" s="15"/>
       <c r="X61" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="62" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S62" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="T62" s="10"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S62" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="T62" s="21"/>
+      <c r="U62" s="21"/>
+      <c r="V62" s="21"/>
+      <c r="W62" s="15"/>
       <c r="X62" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="63" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S63" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S63" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="T63" s="21"/>
+      <c r="U63" s="21"/>
+      <c r="V63" s="21"/>
+      <c r="W63" s="15"/>
       <c r="X63" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S64" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="T64" s="10"/>
-      <c r="U64" s="10"/>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S64" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="T64" s="21"/>
+      <c r="U64" s="21"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="15"/>
       <c r="X64" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S65" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
-      <c r="V65" s="10"/>
-      <c r="W65" s="10"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S65" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="T65" s="21"/>
+      <c r="U65" s="21"/>
+      <c r="V65" s="21"/>
+      <c r="W65" s="15"/>
       <c r="X65" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S66" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="T66" s="10"/>
-      <c r="U66" s="10"/>
-      <c r="V66" s="10"/>
-      <c r="W66" s="10"/>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="19:24" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S66" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="T66" s="21"/>
+      <c r="U66" s="21"/>
+      <c r="V66" s="21"/>
+      <c r="W66" s="15"/>
       <c r="X66" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="67" spans="19:24" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="S67" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
-      <c r="V67" s="10"/>
-      <c r="W67" s="10"/>
-      <c r="X67" s="8" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="124">
+  <mergeCells count="123">
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="S60:W60"/>
-    <mergeCell ref="S61:W61"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="V34:W34"/>
     <mergeCell ref="A2:R2"/>
@@ -2929,10 +3079,10 @@
     <mergeCell ref="V10:W10"/>
     <mergeCell ref="S4:X4"/>
     <mergeCell ref="T3:U3"/>
-    <mergeCell ref="S65:W65"/>
+    <mergeCell ref="S64:W64"/>
     <mergeCell ref="S30:T30"/>
     <mergeCell ref="S20:T20"/>
-    <mergeCell ref="S63:W63"/>
+    <mergeCell ref="S62:W62"/>
     <mergeCell ref="S22:T22"/>
     <mergeCell ref="S12:T12"/>
     <mergeCell ref="V33:W33"/>
@@ -2948,7 +3098,7 @@
     <mergeCell ref="S25:X25"/>
     <mergeCell ref="V17:W17"/>
     <mergeCell ref="S21:T21"/>
-    <mergeCell ref="S67:W67"/>
+    <mergeCell ref="S66:W66"/>
     <mergeCell ref="S36:X36"/>
     <mergeCell ref="M22:Q22"/>
     <mergeCell ref="V9:W9"/>
@@ -2960,11 +3110,11 @@
     <mergeCell ref="S15:T15"/>
     <mergeCell ref="V11:W11"/>
     <mergeCell ref="S33:T33"/>
-    <mergeCell ref="S66:W66"/>
+    <mergeCell ref="S65:W65"/>
     <mergeCell ref="V49:W49"/>
     <mergeCell ref="V27:W27"/>
     <mergeCell ref="S41:T41"/>
-    <mergeCell ref="S62:W62"/>
+    <mergeCell ref="S61:W61"/>
     <mergeCell ref="V40:W40"/>
     <mergeCell ref="S34:T34"/>
     <mergeCell ref="V45:W45"/>
@@ -2977,7 +3127,7 @@
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="S64:W64"/>
+    <mergeCell ref="S63:W63"/>
     <mergeCell ref="M29:Q29"/>
     <mergeCell ref="M38:Q38"/>
     <mergeCell ref="V37:W37"/>
